--- a/data/trans_orig/IP31KM16_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM16_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14491</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5160</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>33,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9641</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5545</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15608</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49657</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64075</t>
+          <t>47027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>108405</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>81749</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>117736</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,21%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>66,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>104610</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>98643</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>108706</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>119190</t>
+          <t>108514</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87158</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131376</t>
+          <t>112781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>223801</t>
+          <t>216919</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186991</t>
+          <t>194467</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>236670</t>
+          <t>227106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27894</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44872</t>
+          <t>35689</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17597</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36295</t>
+          <t>32622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>53711</t>
+          <t>48354</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40431</t>
+          <t>37970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72436</t>
+          <t>62184</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>206061</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>195552</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>214503</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>158220</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>141242</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>166469</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>221703</t>
+          <t>157419</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211225</t>
+          <t>147971</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>229923</t>
+          <t>164327</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>379923</t>
+          <t>363479</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>361198</t>
+          <t>349649</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>393203</t>
+          <t>373863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22117</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15060</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30573</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17673</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9988</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26111</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22734</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15542</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31886</t>
+          <t>25543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>39409</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>30261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52502</t>
+          <t>50860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>144405</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>135949</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>151462</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,64%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,96%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>170576</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>162138</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>178261</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>90,61%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,13%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>160355</t>
+          <t>137745</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151203</t>
+          <t>129495</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167547</t>
+          <t>143190</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>330932</t>
+          <t>282151</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318837</t>
+          <t>270700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>342791</t>
+          <t>291299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25801</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35070</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>31010</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22765</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41405</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27585</t>
+          <t>30069</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19800</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37284</t>
+          <t>39892</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>58595</t>
+          <t>55870</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47643</t>
+          <t>44884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71689</t>
+          <t>68568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>133509</t>
+          <t>140364</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123114</t>
+          <t>131095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141754</t>
+          <t>146888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>149724</t>
+          <t>133910</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140025</t>
+          <t>124087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157509</t>
+          <t>142064</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>283233</t>
+          <t>274274</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>270139</t>
+          <t>261576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>294185</t>
+          <t>285260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>87588</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>70780</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>112471</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>86218</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>69400</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>107035</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,39%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>93761</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76109</t>
+          <t>67528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>130845</t>
+          <t>96009</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>179979</t>
+          <t>168208</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>154711</t>
+          <t>145236</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>215729</t>
+          <t>195757</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>599236</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>574353</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>616044</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,25%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,62%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>800</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>566916</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>546099</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>583734</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>86,8%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,37%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>650972</t>
+          <t>537587</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>613888</t>
+          <t>522199</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>668624</t>
+          <t>550680</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1217888</t>
+          <t>1136823</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1182138</t>
+          <t>1109274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1243156</t>
+          <t>1159795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
